--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260807.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260807.xlsx
@@ -667,17 +667,17 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>443,258,922</t>
+          <t>158,608,963</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -689,17 +689,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>158,608,963</t>
+          <t>443,258,922</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
